--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>VistA Source ValueSet for Terminology Maps VitalsQualifyingDevice</t>
+    <t>VistA Source ValueSet for Terminology Maps VF_VitalsQualifyingDevice</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>VistA Source ValueSet for Terminology Maps VF_VitalsQualifyingDevice</t>
+    <t>VistA Source ValueSet for Terminology Maps [VF_VitalsQualifyingDevice](ConceptMap-VF-VitalsQualifyingDevice)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>VistA Source ValueSet for Terminology Maps [VF_VitalsQualifyingDevice](ConceptMap-VF-VitalsQualifyingDevice)</t>
+    <t>VistA Source ValueSet for Terminology Maps [VF_VitalsQualifyingDevice](ConceptMap-VF-VitalsQualifyingDevice.html)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
+++ b/docs/ValueSet-VitalsQualifyingDevice-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
